--- a/events/LaSeu_2023_WC/LaSeu_2023_WC_start.xlsx
+++ b/events/LaSeu_2023_WC/LaSeu_2023_WC_start.xlsx
@@ -32025,6 +32025,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X537" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -35828,6 +35833,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X593" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -37725,6 +37735,11 @@
       <c r="R621" t="inlineStr">
         <is>
           <t>FISEROVA Tereza</t>
+        </is>
+      </c>
+      <c r="X621" t="inlineStr">
+        <is>
+          <t>42016</t>
         </is>
       </c>
     </row>
